--- a/setup/import-data/eselram-data-import-template.xlsx
+++ b/setup/import-data/eselram-data-import-template.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R75d7c1473347466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="2" r:id="Rdc77b57925254cad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bookings" sheetId="3" r:id="Rb99a5d97ac9949f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packages &amp; Courses" sheetId="4" r:id="R22a4e68735614c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treatment History" sheetId="5" r:id="Ra4bcc8e83d114af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vouchers" sheetId="6" r:id="R3b981a301f664713"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Eselram Setup" sheetId="7" r:id="Rab42085ac432462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R4e62769154484469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="2" r:id="R89d7e9ff39c74826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bookings" sheetId="3" r:id="R7d32560b6b6949b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packages &amp; Courses" sheetId="4" r:id="R01f299f347f7483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treatment History" sheetId="5" r:id="R5852ba039db24c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vouchers" sheetId="6" r:id="Re17d2d75a9604033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Eselram Setup" sheetId="7" r:id="R0350cdd30378415d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -316,7 +316,7 @@
         <x:v>3. Packages &amp; Courses</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Choose the customer's Eselram package/course. Completed booking rows linked to that package/course are what Eselram uses to count used sessions.</x:v>
+        <x:v>Choose the customer's Eselram package/course. If a paid completed consultation was credited to that package, enter it in Consultation credit (£). Completed booking rows linked to that package/course are what Eselram uses to count used sessions.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6514,18 +6514,21 @@
         <x:v>Package price (£)</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
+        <x:v>Consultation credit (£)</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="str">
         <x:v>Amount already paid (£)</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>Payment method</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
+      <x:c r="J1" s="10" t="str">
         <x:v>Discount (£)</x:v>
       </x:c>
-      <x:c r="J1" s="10" t="str">
+      <x:c r="K1" s="10" t="str">
         <x:v>Voucher used</x:v>
       </x:c>
-      <x:c r="K1" s="10" t="str">
+      <x:c r="L1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
